--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R29a49f5007df4b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd70a357a9de4d42"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1511c42077364321"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0c0e49360ed4448"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08f36b188dcd4f48"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0211fc4c68144d7"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfd70a357a9de4d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb695668619604e5f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc0c0e49360ed4448"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f7663e4e755466a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0211fc4c68144d7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2846b7e14884527"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb695668619604e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c890133cb4c409e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2f7663e4e755466a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7481ef45093a4adf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2846b7e14884527"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaafa2713889443e"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c890133cb4c409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22a79cda78144321"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7481ef45093a4adf"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22a2d0e20f4b4b43"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaafa2713889443e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R709102f881e848dd"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22a79cda78144321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd35390a725cf4e38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R22a2d0e20f4b4b43"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbb286aacdd2643b0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R709102f881e848dd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f602933cc964b1d"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd35390a725cf4e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe714fd265364c15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbb286aacdd2643b0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5147ede09dc14ded"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f602933cc964b1d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0569fc8b52425a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbe714fd265364c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb37a0c0b6c5d4163"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5147ede09dc14ded"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31cf3ea21d484a2a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0569fc8b52425a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R843c5fcbbef748fa"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb37a0c0b6c5d4163"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3dd2730c28bd4193"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R31cf3ea21d484a2a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R972b218e79c94615"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R843c5fcbbef748fa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90cce722f4fc47ea"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3dd2730c28bd4193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc8fb7f9fc2f434e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R972b218e79c94615"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re66515eead884730"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90cce722f4fc47ea"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2249a6b89874793"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbc8fb7f9fc2f434e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R823031fa53ba44fb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re66515eead884730"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24c4661b10fd48db"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2249a6b89874793"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77ac24b1e71f429e"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R823031fa53ba44fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cf6cff51e7e44da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24c4661b10fd48db"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91691e00d27743fd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77ac24b1e71f429e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb7f205bbb34d3b"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1cf6cff51e7e44da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8636c532707847a5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R91691e00d27743fd"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcee17f99f1b14c47"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb7f205bbb34d3b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d554905798e4ac1"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8636c532707847a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd400e62775604a93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcee17f99f1b14c47"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf6c65b2e53094806"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d554905798e4ac1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f6825e4ac104cc3"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd400e62775604a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f22a24164f34b2d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf6c65b2e53094806"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R448dfb4dcb0c4b4e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f6825e4ac104cc3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf63c82887ae7426b"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartLine/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f22a24164f34b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2262d053c8eb4cab"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -178,7 +178,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R448dfb4dcb0c4b4e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd5c3dea856c1467e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -235,6 +235,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf63c82887ae7426b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c8d150108b94c85"/>
 </x:worksheet>
 </file>